--- a/fix/narrative-sos/ig/StructureDefinition-sas-sos-slot-aggregator.xlsx
+++ b/fix/narrative-sos/ig/StructureDefinition-sas-sos-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T09:21:44+00:00</t>
+    <t>2026-07-06T09:46:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/narrative-sos/ig/StructureDefinition-sas-sos-slot-aggregator.xlsx
+++ b/fix/narrative-sos/ig/StructureDefinition-sas-sos-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T09:46:17+00:00</t>
+    <t>2026-07-06T09:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
